--- a/Lab2/регистры_лр_2.xlsx
+++ b/Lab2/регистры_лр_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4 сем\ТИ\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9699743D-3017-4891-BD5F-CDCCDFD1E7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FC3B19-3AA9-4F98-9DBF-FDC23DC22D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{93E2E77F-C391-4305-B3E1-E18B01439CEB}"/>
   </bookViews>
@@ -44,13 +44,13 @@
     <t>Степени</t>
   </si>
   <si>
+    <t xml:space="preserve">                              Состояние регистра
+Шаги</t>
+  </si>
+  <si>
     <t>Вариант 10, степень многочлена 32.
 Многочлен:
  x^32 + x^28 + x^27 + x + 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                                      Состояние регистра
-Шаги</t>
   </si>
 </sst>
 </file>
@@ -635,7 +635,7 @@
     <row r="1" spans="2:35" ht="73.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:35" ht="82.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="16" t="s">
         <v>1</v>
@@ -677,7 +677,7 @@
     </row>
     <row r="3" spans="2:35" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="10">
         <v>32</v>

--- a/Lab2/регистры_лр_2.xlsx
+++ b/Lab2/регистры_лр_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4 сем\ТИ\2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0FC3B19-3AA9-4F98-9DBF-FDC23DC22D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7139D00B-4D06-4686-9B10-424566FC2447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{93E2E77F-C391-4305-B3E1-E18B01439CEB}"/>
   </bookViews>
@@ -38,14 +38,14 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
+    <t>Состояние регистра
+Шаги</t>
+  </si>
+  <si>
     <t>XOR</t>
   </si>
   <si>
     <t>Степени</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                              Состояние регистра
-Шаги</t>
   </si>
   <si>
     <t>Вариант 10, степень многочлена 32.
@@ -638,7 +638,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="16"/>
       <c r="E2" s="16"/>
@@ -672,12 +672,12 @@
       <c r="AG2" s="16"/>
       <c r="AH2" s="17"/>
       <c r="AI2" s="6" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="2:35" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3" s="10">
         <v>32</v>
